--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T04:18:11+00:00</t>
+    <t>2024-02-15T10:16:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T10:16:22+00:00</t>
+    <t>2024-02-15T13:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T13:55:36+00:00</t>
+    <t>2024-02-15T15:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T15:16:21+00:00</t>
+    <t>2024-02-15T16:30:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t>No display for ContactDetail</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>FRANCE</t>
   </si>
   <si>
     <t>Description</t>
@@ -233,7 +239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -328,20 +334,28 @@
       <c r="A12" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>21</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>23</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -360,28 +374,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T16:30:29+00:00</t>
+    <t>2024-02-16T04:18:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T04:18:43+00:00</t>
+    <t>2024-02-16T10:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:15:55+00:00</t>
+    <t>2024-02-16T15:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T15:17:56+00:00</t>
+    <t>2024-02-16T16:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T16:44:50+00:00</t>
+    <t>2024-02-16T17:23:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T17:23:45+00:00</t>
+    <t>2024-02-17T04:18:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T04:18:37+00:00</t>
+    <t>2024-02-17T10:14:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T10:14:29+00:00</t>
+    <t>2024-02-17T15:16:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T15:16:06+00:00</t>
+    <t>2024-02-18T04:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T04:16:49+00:00</t>
+    <t>2024-02-18T10:15:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T10:15:42+00:00</t>
+    <t>2024-02-18T15:16:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T15:16:08+00:00</t>
+    <t>2024-02-19T04:19:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T04:19:20+00:00</t>
+    <t>2024-02-19T10:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T10:16:40+00:00</t>
+    <t>2024-02-19T15:15:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T15:15:42+00:00</t>
+    <t>2024-02-20T04:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-20T04:18:33+00:00</t>
+    <t>2024-02-20T10:16:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-20T10:16:59+00:00</t>
+    <t>2024-02-20T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-20T15:16:54+00:00</t>
+    <t>2024-02-20T18:25:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-20T18:25:57+00:00</t>
+    <t>2024-02-21T04:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-21T04:17:52+00:00</t>
+    <t>2024-02-21T15:16:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-21T15:16:29+00:00</t>
+    <t>2024-02-22T04:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-22T04:16:57+00:00</t>
+    <t>2024-02-22T10:15:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-22T10:15:41+00:00</t>
+    <t>2024-02-22T15:15:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-22T15:15:52+00:00</t>
+    <t>2024-02-23T04:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T04:17:13+00:00</t>
+    <t>2024-02-23T10:17:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T10:17:00+00:00</t>
+    <t>2024-02-24T04:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-24T04:17:45+00:00</t>
+    <t>2024-02-24T10:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-24T10:16:05+00:00</t>
+    <t>2024-02-24T14:51:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-24T14:51:36+00:00</t>
+    <t>2024-02-24T15:15:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-24T15:15:18+00:00</t>
+    <t>2024-02-24T15:36:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-24T15:36:52+00:00</t>
+    <t>2024-02-25T04:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-25T04:18:09+00:00</t>
+    <t>2024-02-25T10:15:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-25T10:15:19+00:00</t>
+    <t>2024-02-25T15:14:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-25T15:14:15+00:00</t>
+    <t>2024-02-26T04:17:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T04:17:31+00:00</t>
+    <t>2024-02-26T10:16:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T10:16:46+00:00</t>
+    <t>2024-02-26T15:16:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T15:16:22+00:00</t>
+    <t>2024-02-27T04:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-27T04:18:04+00:00</t>
+    <t>2024-02-27T10:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-27T10:18:54+00:00</t>
+    <t>2024-02-27T15:17:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-27T15:17:04+00:00</t>
+    <t>2024-02-28T04:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T04:18:15+00:00</t>
+    <t>2024-02-28T10:15:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T10:15:13+00:00</t>
+    <t>2024-02-28T15:14:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T15:14:00+00:00</t>
+    <t>2024-02-29T04:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-29T04:18:21+00:00</t>
+    <t>2024-02-29T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-JDV-cipucd-all.xlsx
+++ b/ig/main/ValueSet-JDV-cipucd-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-29T10:15:47+00:00</t>
+    <t>2024-02-29T15:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
